--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_323_R33.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_323_R33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5911</v>
+        <v>4.251</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7881</v>
+        <v>5.6832</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.197</v>
+        <v>-1.4323</v>
       </c>
       <c r="G2" t="n">
         <v>6.4881</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9253</v>
+        <v>1.5852</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4629</v>
+        <v>0.358</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4624</v>
+        <v>1.2272</v>
       </c>
       <c r="V2" t="n">
         <v>-3.3584</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6363</v>
+        <v>4.2507</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1878</v>
+        <v>1.9702</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4485</v>
+        <v>2.2805</v>
       </c>
       <c r="G3" t="n">
         <v>2.5663</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0022</v>
+        <v>0.6122</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1949</v>
+        <v>-0.4125</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1927</v>
+        <v>1.0247</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1303</v>
+        <v>3.2221</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8654</v>
+        <v>3.0581</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2648</v>
+        <v>0.164</v>
       </c>
       <c r="G4" t="n">
         <v>2.971</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0004</v>
+        <v>0.0914</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5228</v>
+        <v>-0.3301</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5223</v>
+        <v>0.4215</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5361</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9911</v>
+        <v>1.0083</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2143</v>
+        <v>-0.0963</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2054</v>
+        <v>1.1046</v>
       </c>
       <c r="G5" t="n">
         <v>-2.9515</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>0.829</v>
+        <v>0.8461</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0351</v>
+        <v>0.0828</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8641</v>
+        <v>0.7633</v>
       </c>
       <c r="V5" t="n">
         <v>5.8971</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5364</v>
+        <v>0.6783</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8447</v>
+        <v>-0.77</v>
       </c>
       <c r="F6" t="n">
-        <v>1.381</v>
+        <v>1.4483</v>
       </c>
       <c r="G6" t="n">
         <v>1.5845</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3435</v>
+        <v>0.4854</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2592</v>
+        <v>-0.1845</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6027</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.324</v>
+        <v>0.6099</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4019</v>
+        <v>0.5199</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.078</v>
+        <v>0.0901</v>
       </c>
       <c r="G7" t="n">
         <v>0.1293</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2693</v>
+        <v>0.0167</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0452</v>
+        <v>0.1228</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.32</v>
+        <v>-1.4881</v>
       </c>
       <c r="E8" t="n">
         <v>-1.2607</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0594</v>
+        <v>-0.2274</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3958</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2535</v>
+        <v>0.0854</v>
       </c>
       <c r="T8" t="n">
         <v>-0.224</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4775</v>
+        <v>0.3095</v>
       </c>
       <c r="V8" t="n">
         <v>0.6778999999999999</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7852</v>
+        <v>-1.6262</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9914</v>
+        <v>-2.8426</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7938</v>
+        <v>1.2163</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6404</v>
+        <v>-1.6145</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4693</v>
+        <v>-1.3602</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1711</v>
+        <v>-0.2542</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6823</v>
+        <v>-1.1748</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0672</v>
+        <v>-0.9271</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.2477</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9581</v>
+        <v>-0.4397</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5365</v>
+        <v>-0.4331</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4216</v>
+        <v>-0.0065</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9278</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R9" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.217</v>
+        <v>0.1454</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1494</v>
+        <v>-0.1885</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0677</v>
+        <v>0.3339</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.4665</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9463</v>
+        <v>-2.5328</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6249</v>
+        <v>-1.8735</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6786</v>
+        <v>-0.6593</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6145</v>
+        <v>-1.6404</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3602</v>
+        <v>-0.4693</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2542</v>
+        <v>-1.1711</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1748</v>
+        <v>-0.6823</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9271</v>
+        <v>0.0672</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2477</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4397</v>
+        <v>-0.9581</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4331</v>
+        <v>-0.5365</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0065</v>
+        <v>-0.4216</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6237</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1747</v>
+        <v>0.0354</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9709</v>
+        <v>-0.0314</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2038</v>
+        <v>0.0668</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4665</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7485</v>
+        <v>-4.5907</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0547</v>
+        <v>-3.7625</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6938</v>
+        <v>-0.8282</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0455</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4594</v>
+        <v>0.6172</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9006</v>
+        <v>0.1928</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5588</v>
+        <v>0.4244</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9304</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.409200000000001</v>
+        <v>3.782499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2525000000000004</v>
+        <v>0.6258000000000017</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1563</v>
+        <v>3.1566</v>
       </c>
       <c r="G12" t="n">
         <v>3.091500000000003</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8400999999999998</v>
+        <v>-0.8401000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>3.9317</v>
@@ -1366,7 +1366,7 @@
         <v>8.561299999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>4.061700000000001</v>
+        <v>4.0617</v>
       </c>
       <c r="L12" t="n">
         <v>4.499499999999999</v>
@@ -1378,7 +1378,7 @@
         <v>-4.902</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5678</v>
+        <v>-0.5677999999999999</v>
       </c>
       <c r="P12" t="n">
         <v>-8.1183</v>
@@ -1390,13 +1390,13 @@
         <v>8.118399999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1471</v>
+        <v>4.5204</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2168</v>
+        <v>-0.8435</v>
       </c>
       <c r="U12" t="n">
-        <v>5.363799999999999</v>
+        <v>5.364</v>
       </c>
       <c r="V12" t="n">
         <v>4.2888</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7373</v>
+        <v>5.1646</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4646</v>
+        <v>2.9928</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2726</v>
+        <v>2.1718</v>
       </c>
       <c r="G13" t="n">
         <v>1.1625</v>
@@ -1468,13 +1468,13 @@
         <v>2.5515</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.3785</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1968</v>
+        <v>-0.275</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7543</v>
+        <v>0.6535</v>
       </c>
       <c r="V13" t="n">
         <v>1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5673</v>
+        <v>3.3555</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2176</v>
+        <v>2.5099</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3497</v>
+        <v>0.8456</v>
       </c>
       <c r="G14" t="n">
         <v>2.0712</v>
@@ -1546,13 +1546,13 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8905</v>
+        <v>-0.3213</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0123</v>
+        <v>-0.6954</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8782</v>
+        <v>0.3741</v>
       </c>
       <c r="V14" t="n">
         <v>0.6778999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.715</v>
+        <v>1.9838</v>
       </c>
       <c r="E15" t="n">
         <v>-0.2631</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9781</v>
+        <v>2.2469</v>
       </c>
       <c r="G15" t="n">
         <v>0.8987000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5755</v>
+        <v>-0.3066</v>
       </c>
       <c r="T15" t="n">
         <v>-0.3576</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2179</v>
+        <v>0.051</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4997</v>
+        <v>1.7692</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5946</v>
+        <v>1.8305</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0949</v>
+        <v>-0.0613</v>
       </c>
       <c r="G16" t="n">
         <v>0.6008</v>
@@ -1702,13 +1702,13 @@
         <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2788</v>
+        <v>-1.0093</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1044</v>
+        <v>-0.8685</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1744</v>
+        <v>-0.1408</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1418</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3394</v>
+        <v>0.0982</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.1392</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2427</v>
+        <v>-0.0411</v>
       </c>
       <c r="G17" t="n">
         <v>0.299</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5456</v>
+        <v>-0.1081</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5975</v>
+        <v>-0.3615</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0518</v>
+        <v>0.2535</v>
       </c>
       <c r="V17" t="n">
         <v>-0.7886</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.851</v>
+        <v>-0.8174</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1158</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7353</v>
+        <v>-0.7016</v>
       </c>
       <c r="G18" t="n">
         <v>-0.188</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.127</v>
+        <v>-0.0934</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5361</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>I. CORDINIER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3921</v>
+        <v>-1.6292</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6698</v>
+        <v>-1.7956</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0618</v>
+        <v>0.1664</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8042</v>
+        <v>-1.5025</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7345</v>
+        <v>-0.6158</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9303</v>
+        <v>-0.8867</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9339</v>
+        <v>-0.7412</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6502</v>
+        <v>-0.383</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7163</v>
+        <v>-0.3581</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1298</v>
+        <v>-0.7613</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9157</v>
+        <v>-0.2327</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.214</v>
+        <v>-0.5286</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4121</v>
+        <v>-0.5906</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0553</v>
+        <v>-0.735</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3567</v>
+        <v>0.1443</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. CORDINIER</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9659</v>
+        <v>-1.8296</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0315</v>
+        <v>0.4339</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06560000000000001</v>
+        <v>-2.2635</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5025</v>
+        <v>1.8042</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6158</v>
+        <v>2.7345</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8867</v>
+        <v>-0.9303</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7412</v>
+        <v>2.9339</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.383</v>
+        <v>3.6502</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3581</v>
+        <v>-0.7163</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7613</v>
+        <v>-1.1298</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2327</v>
+        <v>-0.9157</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5286</v>
+        <v>-0.214</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9274</v>
+        <v>-0.0255</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9709</v>
+        <v>-0.1806</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0435</v>
+        <v>0.1551</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3129</v>
+        <v>-2.2286</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1403</v>
+        <v>-1.0224</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1726</v>
+        <v>-1.2062</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3009</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4037</v>
+        <v>-0.3194</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1937</v>
+        <v>0.1601</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9284</v>
+        <v>-4.5409</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9912</v>
+        <v>-3.6373</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9372</v>
+        <v>-0.9036</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0489</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3614</v>
+        <v>-0.9739</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0297</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3317</v>
+        <v>-0.2981</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7501</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1385</v>
+        <v>-4.7346</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6063</v>
+        <v>-4.3704</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5322</v>
+        <v>-0.3642</v>
       </c>
       <c r="G23" t="n">
         <v>-4.8877</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1813</v>
+        <v>-0.7773</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8215</v>
+        <v>-0.5856</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3598</v>
+        <v>-0.1918</v>
       </c>
       <c r="V23" t="n">
         <v>0.9304</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.408899999999997</v>
+        <v>-3.409000000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.298299999999999</v>
+        <v>-3.298300000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1107000000000002</v>
+        <v>-0.1108</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0916</v>
@@ -2326,13 +2326,13 @@
         <v>16.2367</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.147</v>
+        <v>-4.1469</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.364100000000001</v>
+        <v>-5.364</v>
       </c>
       <c r="U24" t="n">
-        <v>1.2168</v>
+        <v>1.2169</v>
       </c>
       <c r="V24" t="n">
         <v>-4.288800000000001</v>
